--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -1128,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Patrik Nygren, Mikael Hägg</t>
+          <t>Mikael Hägg, Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mikael Hägg, Patrik Nygren</t>
+          <t>Patrik Nygren, Mikael Hägg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -1841,11 +1841,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1956,11 +1952,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93473</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90951</v>
+        <v>90963</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90963</v>
+        <v>90964</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90964</v>
+        <v>90967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>91190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93489</v>
+        <v>93490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93511</v>
+        <v>93512</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90967</v>
+        <v>90968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 27804-2026 artfynd.xlsx
+++ b/artfynd/A 27804-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136979006</v>
       </c>
       <c r="B2" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>136979272</v>
       </c>
       <c r="B3" t="n">
-        <v>91190</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>136979080</v>
       </c>
       <c r="B4" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136979366</v>
       </c>
       <c r="B5" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>136979382</v>
       </c>
       <c r="B6" t="n">
-        <v>93490</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>136979393</v>
       </c>
       <c r="B7" t="n">
-        <v>93512</v>
+        <v>93515</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>136979296</v>
       </c>
       <c r="B8" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>136979090</v>
       </c>
       <c r="B9" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>136979467</v>
       </c>
       <c r="B10" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136979506</v>
       </c>
       <c r="B11" t="n">
-        <v>90968</v>
+        <v>90971</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>136979039</v>
       </c>
       <c r="B12" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>136979532</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
